--- a/output/pdf_financials_xlsx/TGIF.xlsx
+++ b/output/pdf_financials_xlsx/TGIF.xlsx
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.449184</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.545977</v>
       </c>
     </row>
     <row r="35">
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.449184</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.545977</v>
       </c>
     </row>
     <row r="37">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.249633</v>
+        <v>0.800449</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.461431</v>
+        <v>0.915454</v>
       </c>
     </row>
     <row r="49">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">

--- a/output/pdf_financials_xlsx/TGIF.xlsx
+++ b/output/pdf_financials_xlsx/TGIF.xlsx
@@ -690,11 +690,15 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>-0.329619</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>0.016019</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -704,10 +708,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.329619</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>0.016019</v>
       </c>
     </row>
     <row r="22">
@@ -1265,10 +1269,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>3.944674</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>3.001919</v>
       </c>
     </row>
     <row r="65">
@@ -1304,10 +1308,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.8147</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.370182</v>
       </c>
     </row>
     <row r="68">
@@ -1861,10 +1865,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.143475</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.265015</v>
       </c>
     </row>
     <row r="111">
@@ -2980,7 +2984,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.143475</v>
       </c>
@@ -4548,7 +4556,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
